--- a/data/trans_dic/CAGE_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,57</t>
+          <t>0,39; 1,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,15</t>
+          <t>1,01; 3,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,6</t>
+          <t>1,31; 3,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 9,95</t>
+          <t>3,46; 9,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,89</t>
+          <t>0,24; 0,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,29</t>
+          <t>0,44; 1,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,65</t>
+          <t>0,59; 1,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,18</t>
+          <t>3,02; 8,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,39</t>
+          <t>0,43; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,88</t>
+          <t>1,57; 2,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,02</t>
+          <t>0,92; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,19</t>
+          <t>0,69; 2,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,66</t>
+          <t>0,06; 0,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,66</t>
+          <t>0,11; 0,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,84</t>
+          <t>0,22; 0,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,71</t>
+          <t>0,42; 2,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,85</t>
+          <t>0,33; 0,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,66</t>
+          <t>0,93; 1,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,29</t>
+          <t>0,63; 1,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,03</t>
+          <t>0,72; 1,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,77</t>
+          <t>0,15; 1,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,25</t>
+          <t>0,24; 3,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,61</t>
+          <t>0,17; 2,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,69</t>
+          <t>1,29; 4,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,67</t>
+          <t>0,51; 2,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,03</t>
+          <t>0,53; 3,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,22</t>
+          <t>0,18; 1,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,06</t>
+          <t>0,18; 1,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,89</t>
+          <t>0,45; 1,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,22</t>
+          <t>1,15; 3,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,19</t>
+          <t>0,52; 1,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,52</t>
+          <t>1,47; 2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,94</t>
+          <t>1,1; 1,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,19</t>
+          <t>1,64; 3,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,52</t>
+          <t>0,13; 0,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,34</t>
+          <t>0,06; 0,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,76</t>
+          <t>0,27; 0,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,35</t>
+          <t>0,56; 2,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,73</t>
+          <t>0,36; 0,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,3</t>
+          <t>0,79; 1,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,24</t>
+          <t>0,74; 1,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,47</t>
+          <t>1,27; 2,48</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3887; 16195</t>
+          <t>4023; 16740</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10036; 30709</t>
+          <t>9885; 30574</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9289; 27119</t>
+          <t>9847; 27525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8136; 24200</t>
+          <t>8405; 24239</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 10563</t>
+          <t>0; 11928</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7244</t>
+          <t>0; 5779</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5860; 20845</t>
+          <t>5568; 21599</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9770; 29808</t>
+          <t>10070; 30480</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10086; 28779</t>
+          <t>10384; 30224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9395; 25413</t>
+          <t>9367; 25937</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8086; 23535</t>
+          <t>7266; 22502</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31012; 56559</t>
+          <t>30748; 56382</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19192; 41897</t>
+          <t>19147; 41441</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6715; 21445</t>
+          <t>6733; 21216</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1168; 10518</t>
+          <t>1014; 10303</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2007; 11642</t>
+          <t>1998; 12318</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4386; 16707</t>
+          <t>4338; 17417</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2461; 19096</t>
+          <t>2990; 19195</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10657; 27764</t>
+          <t>10948; 27987</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35262; 61678</t>
+          <t>34463; 61318</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27066; 52542</t>
+          <t>25506; 49955</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12752; 34262</t>
+          <t>12214; 33351</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>850; 9753</t>
+          <t>848; 9628</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1710; 15621</t>
+          <t>1143; 14465</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>959; 14288</t>
+          <t>957; 12589</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4458; 16088</t>
+          <t>4427; 15656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7767</t>
+          <t>0; 7185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2793; 14658</t>
+          <t>2796; 14518</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1224; 7299</t>
+          <t>1272; 7348</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1993; 12498</t>
+          <t>1883; 12812</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1985; 19383</t>
+          <t>1699; 15702</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4807; 20693</t>
+          <t>4947; 20051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6644; 18837</t>
+          <t>6688; 19326</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17045; 38902</t>
+          <t>17014; 38046</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50690; 86263</t>
+          <t>50228; 84968</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35584; 65569</t>
+          <t>37090; 65170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25553; 50066</t>
+          <t>25651; 50099</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3720; 17659</t>
+          <t>4326; 18367</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1991; 11984</t>
+          <t>1993; 11312</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9651; 26771</t>
+          <t>9368; 27603</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6134; 23820</t>
+          <t>5711; 22873</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24809; 48344</t>
+          <t>24204; 47707</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55309; 90328</t>
+          <t>54981; 89996</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49924; 85389</t>
+          <t>50793; 84445</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32572; 63738</t>
+          <t>32691; 63974</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/CAGE_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,62</t>
+          <t>0,38; 1,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,14</t>
+          <t>1,08; 3,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,65</t>
+          <t>1,14; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,96</t>
+          <t>3,54; 9,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,92</t>
+          <t>0,26; 0,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,73</t>
+          <t>0,58; 1,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,35</t>
+          <t>2,83; 7,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,33</t>
+          <t>0,45; 1,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,87</t>
+          <t>1,52; 2,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,0</t>
+          <t>0,92; 1,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,16</t>
+          <t>0,8; 2,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,65</t>
+          <t>0,07; 0,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,7</t>
+          <t>0,11; 0,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,88</t>
+          <t>0,25; 0,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,73</t>
+          <t>0,97; 4,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,85</t>
+          <t>0,33; 0,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,65</t>
+          <t>0,97; 1,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,23</t>
+          <t>0,67; 1,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,98</t>
+          <t>1,08; 2,51</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,75</t>
+          <t>0,15; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,01</t>
+          <t>0,36; 3,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,3</t>
+          <t>0,18; 2,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,57</t>
+          <t>1,66; 4,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,64</t>
+          <t>0,51; 2,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,05</t>
+          <t>0,55; 3,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,25</t>
+          <t>0,18; 1,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,67</t>
+          <t>0,18; 1,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,83</t>
+          <t>0,45; 1,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,31</t>
+          <t>1,46; 3,71</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,16</t>
+          <t>0,51; 1,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,48</t>
+          <t>1,48; 2,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,93</t>
+          <t>1,04; 1,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,2</t>
+          <t>1,78; 3,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,54</t>
+          <t>0,14; 0,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,78</t>
+          <t>0,3; 0,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,26</t>
+          <t>1,09; 3,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,72</t>
+          <t>0,38; 0,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,29</t>
+          <t>0,77; 1,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,22</t>
+          <t>0,74; 1,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,48</t>
+          <t>1,7; 2,95</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15853</t>
         </is>
       </c>
     </row>
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4023; 16740</t>
+          <t>3956; 17246</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9885; 30574</t>
+          <t>10489; 32276</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9847; 27525</t>
+          <t>8618; 26412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8405; 24239</t>
+          <t>9135; 24102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 11928</t>
+          <t>0; 10790</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5779</t>
+          <t>0; 7139</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5568; 21599</t>
+          <t>6022; 21138</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10070; 30480</t>
+          <t>10137; 30537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10384; 30224</t>
+          <t>10156; 28166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9367; 25937</t>
+          <t>9420; 24956</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>26866</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7266; 22502</t>
+          <t>7661; 23016</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30748; 56382</t>
+          <t>29936; 55764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19147; 41441</t>
+          <t>19115; 41179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6733; 21216</t>
+          <t>8350; 27202</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1014; 10303</t>
+          <t>1169; 10126</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1998; 12318</t>
+          <t>2001; 11245</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4338; 17417</t>
+          <t>4873; 18574</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2990; 19195</t>
+          <t>5362; 22151</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10948; 27987</t>
+          <t>10915; 27289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34463; 61318</t>
+          <t>35916; 62289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25506; 49955</t>
+          <t>27436; 50216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12214; 33351</t>
+          <t>17197; 40064</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>15138</t>
         </is>
       </c>
     </row>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>848; 9628</t>
+          <t>847; 9325</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1143; 14465</t>
+          <t>1715; 16235</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>957; 12589</t>
+          <t>971; 14350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4427; 15656</t>
+          <t>6091; 18197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7185</t>
+          <t>0; 6216</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,32 +1950,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2796; 14518</t>
+          <t>2807; 15074</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1272; 7348</t>
+          <t>1469; 8668</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1883; 12812</t>
+          <t>1880; 13172</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1699; 15702</t>
+          <t>1722; 15873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4947; 20051</t>
+          <t>4883; 20312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6688; 19326</t>
+          <t>9202; 23419</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>57858</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17014; 38046</t>
+          <t>16852; 37973</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50228; 84968</t>
+          <t>50485; 84487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37090; 65170</t>
+          <t>35015; 63766</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25651; 50099</t>
+          <t>29559; 55076</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4326; 18367</t>
+          <t>4632; 18511</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1993; 11312</t>
+          <t>2001; 11416</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9368; 27603</t>
+          <t>10455; 28255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5711; 22873</t>
+          <t>9748; 28289</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24204; 47707</t>
+          <t>24974; 48973</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54981; 89996</t>
+          <t>54042; 89752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50793; 84445</t>
+          <t>50988; 83179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32691; 63974</t>
+          <t>43483; 75582</t>
         </is>
       </c>
     </row>
